--- a/Tests/g17_setup1_with_1ed_sim_outputs.xlsx
+++ b/Tests/g17_setup1_with_1ed_sim_outputs.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="I1" t="n">
-        <v>3160.296349178773</v>
+        <v>3527.846011939817</v>
       </c>
       <c r="J1" t="inlineStr">
         <is>
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="K1" t="n">
-        <v>59.02441188320518</v>
+        <v>2349.197055780402</v>
       </c>
       <c r="L1" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="M1" t="n">
-        <v>27250.68447063304</v>
+        <v>20389.95873640676</v>
       </c>
     </row>
     <row r="2">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3316.064824346746</v>
+        <v>3869.413757949353</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>56.87332554720342</v>
+        <v>3107.920902543701</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>29970.00729409792</v>
+        <v>16043.89765703096</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3428.92615750902</v>
+        <v>3576.247713300155</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>60.19994493946433</v>
+        <v>2704.309233948559</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>24808.61110525485</v>
+        <v>13999.5218222416</v>
       </c>
     </row>
     <row r="4">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3182.366199608689</v>
+        <v>3509.852202783888</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>57.41541673615575</v>
+        <v>2814.6870049434</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>20238.89758048207</v>
+        <v>15403.81631825026</v>
       </c>
     </row>
     <row r="5">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3040.721233797079</v>
+        <v>3691.753295336427</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>63.5209624543786</v>
+        <v>2882.631588641554</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>20794.12405123189</v>
+        <v>18140.11300096288</v>
       </c>
     </row>
     <row r="6">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3135.924618098682</v>
+        <v>2998.619339842266</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>52.54934802278876</v>
+        <v>2401.329653117806</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -706,7 +706,56 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>20101.71023960784</v>
+        <v>19702.77653491014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>---&gt; DER:</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>---&gt; Avg Latency:</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3238.81564504226</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>---&gt; Min Latency:</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2018.414872050285</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>---&gt; Max Latency:</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>4398.857166342437</v>
       </c>
     </row>
   </sheetData>
